--- a/Employee_Reports_wi52/Quennan Carandang Cuesta Q0606.xlsx
+++ b/Employee_Reports_wi52/Quennan Carandang Cuesta Q0606.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-29</v>
+        <v>-37</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1206,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-23</v>
+        <v>-31</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-23</v>
+        <v>-31</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
